--- a/artfynd/A 59286-2025 artfynd.xlsx
+++ b/artfynd/A 59286-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6841531</v>
+        <v>79010646</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hult 800 m NNO, Srm</t>
+          <t>Nykärret, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>610314.9162884604</v>
+        <v>610111</v>
       </c>
       <c r="R2" t="n">
-        <v>6575702.01192464</v>
+        <v>6575450</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-06-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-06-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,68 +777,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6841530</v>
+        <v>93155461</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>220075</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hult 950 m NNO, Srm</t>
+          <t>Nykärret, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610372.2170895146</v>
+        <v>610116</v>
       </c>
       <c r="R3" t="n">
-        <v>6575861.038051208</v>
+        <v>6575440</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,27 +844,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-06-27</t>
+          <t>2021-05-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-06-27</t>
+          <t>2021-05-08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>täcker 1 m2</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,80 +874,68 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bernt Andersson</t>
+          <t>Björn Carlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bernt Andersson</t>
+          <t>Björn Carlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6841528</v>
+        <v>108639101</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>220075</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hult 900 m NNO, Srm</t>
+          <t>Nykärret, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610336.8993742067</v>
+        <v>610097</v>
       </c>
       <c r="R4" t="n">
-        <v>6575808.409549133</v>
+        <v>6575359</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,27 +959,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-06-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-06-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>täcker 2 m2</t>
+          <t>2023-04-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,6 +973,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1061,12 +995,7 @@
         <v>6841527</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610314.9162884604</v>
+        <v>610315</v>
       </c>
       <c r="R5" t="n">
-        <v>6575702.01192464</v>
+        <v>6575702</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1146,19 +1075,9 @@
           <t>2013-06-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-06-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1190,15 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16531343</v>
+        <v>6841528</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1139,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1235,23 +1149,23 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hult 900m NNO, Srm</t>
+          <t>Hult 900 m NNO, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>610397.5587010672</v>
+        <v>610337</v>
       </c>
       <c r="R6" t="n">
-        <v>6575816.816707507</v>
+        <v>6575808</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1275,22 +1189,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-08-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-06-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-08-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-06-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>täcker 2 m2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,56 +1226,63 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16531347</v>
+        <v>6841530</v>
       </c>
       <c r="B7" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hult 900m NNO, Srm</t>
+          <t>Hult 950 m NNO, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>610397.5587010672</v>
+        <v>610372</v>
       </c>
       <c r="R7" t="n">
-        <v>6575816.816707507</v>
+        <v>6575861</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1390,22 +1306,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2014-08-22</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-06-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2014-08-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-06-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>täcker 1 m2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,15 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69866859</v>
+        <v>16531343</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1373,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1477,23 +1383,23 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hult 900 m nno, Srm</t>
+          <t>Hult 900m NNO, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>610397.5141184248</v>
+        <v>610398</v>
       </c>
       <c r="R8" t="n">
-        <v>6575818.34811227</v>
+        <v>6575817</v>
       </c>
       <c r="S8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1515,34 +1421,14 @@
           <t>Länna</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>D-Str-0232</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-08-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-08-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 dellokaler 51+12</t>
+          <t>2014-08-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1553,21 +1439,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Bernt Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1575,69 +1451,67 @@
           <t>Bernt Andersson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>79010639</v>
+        <v>69866859</v>
       </c>
       <c r="B9" t="n">
-        <v>101323</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222395</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nykärret, Srm</t>
+          <t>Hult 900 m nno, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>610111.3715577684</v>
+        <v>610398</v>
       </c>
       <c r="R9" t="n">
-        <v>6575449.827670487</v>
+        <v>6575818</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1659,24 +1533,24 @@
           <t>Länna</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D-Str-0232</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-07-20</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-07-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2 dellokaler 51+12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1685,34 +1559,42 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
           <t>Bernt Andersson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Bernt Andersson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>79010616</v>
       </c>
       <c r="B10" t="n">
-        <v>103088</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106061</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610111.3715577684</v>
+        <v>610111</v>
       </c>
       <c r="R10" t="n">
-        <v>6575449.827670487</v>
+        <v>6575450</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1781,19 +1663,9 @@
           <t>2019-07-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-07-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1818,6 +1690,316 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6841531</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hult 800 m NNO, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>610315</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6575702</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Länna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2013-06-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2013-06-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bernt Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bernt Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>16531347</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hult 900m NNO, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>610398</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6575817</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Länna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2014-08-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2014-08-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bernt Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bernt Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>79010639</v>
+      </c>
+      <c r="B13" t="n">
+        <v>104253</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nykärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>610111</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6575450</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Länna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2019-07-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2019-07-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bernt Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bernt Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59286-2025 artfynd.xlsx
+++ b/artfynd/A 59286-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79010646</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93155461</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108639101</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6841527</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6841528</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6841530</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1452,6 +1487,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16531343</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1586,6 +1626,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69866859</t>
         </is>
       </c>
     </row>
@@ -1690,6 +1735,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79010616</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1794,6 +1844,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6841531</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1894,6 +1949,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16531347</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2000,8 +2060,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79010639</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>